--- a/output/Plan/DeepSeek-V3/feedback results/task_analysis_results_nofeed_Plan_DeepSeek-V3_meeting_feedback_v1.xlsx
+++ b/output/Plan/DeepSeek-V3/feedback results/task_analysis_results_nofeed_Plan_DeepSeek-V3_meeting_feedback_v1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/laiqimei/Desktop/Academic/UPenn/CCB Lab/Project/calendar-planning/output/Plan/DeepSeek-V3/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/laiqimei/Desktop/Academic/UPenn/CCB Lab/Project/calendar-planning/output/Plan/DeepSeek-V3/feedback results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{032CCC2C-9486-3645-B088-524CC9428F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A9FAD68-9C21-304E-B475-F8F984AAC55F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4100" yWindow="760" windowWidth="30240" windowHeight="17680" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11180" yWindow="1620" windowWidth="30240" windowHeight="17580" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
@@ -22,9 +22,8 @@
   </definedNames>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="174" r:id="rId4"/>
+    <pivotCache cacheId="38" r:id="rId4"/>
   </pivotCaches>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -4434,7 +4433,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -4443,7 +4442,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4893,7 +4891,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B1C350DF-D9D2-5140-B69F-D02E12DC9EA8}" name="PivotTable37" cacheId="174" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B1C350DF-D9D2-5140-B69F-D02E12DC9EA8}" name="PivotTable37" cacheId="38" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField dataField="1" showAll="0"/>
@@ -5249,7 +5247,7 @@
       <c r="A4" s="3">
         <v>1</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4">
         <v>66</v>
       </c>
     </row>
@@ -5257,7 +5255,7 @@
       <c r="A5" s="3">
         <v>2</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5">
         <v>31</v>
       </c>
     </row>
@@ -5265,7 +5263,7 @@
       <c r="A6" s="3">
         <v>3</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6">
         <v>2</v>
       </c>
     </row>
@@ -5273,7 +5271,7 @@
       <c r="A7" s="3">
         <v>4</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7">
         <v>1</v>
       </c>
     </row>
@@ -5281,7 +5279,7 @@
       <c r="A8" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8">
         <v>100</v>
       </c>
     </row>
@@ -6110,6 +6108,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:G139"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -6461,7 +6460,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>67</v>
       </c>
@@ -6484,7 +6483,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>67</v>
       </c>
@@ -6691,7 +6690,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>74</v>
       </c>
@@ -6714,7 +6713,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>74</v>
       </c>
@@ -6737,7 +6736,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>49</v>
       </c>
@@ -6760,7 +6759,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>49</v>
       </c>
@@ -6852,7 +6851,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>2</v>
       </c>
@@ -6875,7 +6874,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>2</v>
       </c>
@@ -6898,7 +6897,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>59</v>
       </c>
@@ -6921,7 +6920,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>59</v>
       </c>
@@ -7036,7 +7035,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>40</v>
       </c>
@@ -7059,7 +7058,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>40</v>
       </c>
@@ -7197,7 +7196,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>32</v>
       </c>
@@ -7220,7 +7219,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>32</v>
       </c>
@@ -7243,7 +7242,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>32</v>
       </c>
@@ -7266,7 +7265,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>32</v>
       </c>
@@ -7634,7 +7633,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>81</v>
       </c>
@@ -7657,7 +7656,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>81</v>
       </c>
@@ -7818,7 +7817,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>87</v>
       </c>
@@ -7841,7 +7840,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>87</v>
       </c>
@@ -7864,7 +7863,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>61</v>
       </c>
@@ -7887,7 +7886,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>61</v>
       </c>
@@ -7910,7 +7909,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>61</v>
       </c>
@@ -7933,7 +7932,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>52</v>
       </c>
@@ -7956,7 +7955,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>52</v>
       </c>
@@ -7979,7 +7978,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>95</v>
       </c>
@@ -8002,7 +8001,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>95</v>
       </c>
@@ -8025,7 +8024,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>42</v>
       </c>
@@ -8048,7 +8047,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>42</v>
       </c>
@@ -8094,7 +8093,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>48</v>
       </c>
@@ -8117,7 +8116,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>48</v>
       </c>
@@ -8163,7 +8162,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>23</v>
       </c>
@@ -8186,7 +8185,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>23</v>
       </c>
@@ -8255,7 +8254,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>26</v>
       </c>
@@ -8278,7 +8277,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>26</v>
       </c>
@@ -8301,7 +8300,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>79</v>
       </c>
@@ -8324,7 +8323,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>79</v>
       </c>
@@ -8347,7 +8346,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>27</v>
       </c>
@@ -8370,7 +8369,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>27</v>
       </c>
@@ -8393,7 +8392,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>85</v>
       </c>
@@ -8416,7 +8415,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>85</v>
       </c>
@@ -8508,7 +8507,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>10</v>
       </c>
@@ -8531,7 +8530,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>10</v>
       </c>
@@ -8554,7 +8553,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>17</v>
       </c>
@@ -8577,7 +8576,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>17</v>
       </c>
@@ -8600,7 +8599,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>78</v>
       </c>
@@ -8623,7 +8622,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>78</v>
       </c>
@@ -8646,7 +8645,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>50</v>
       </c>
@@ -8669,7 +8668,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>50</v>
       </c>
@@ -8692,7 +8691,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>56</v>
       </c>
@@ -8715,7 +8714,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>56</v>
       </c>
@@ -8738,7 +8737,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>57</v>
       </c>
@@ -8761,7 +8760,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>57</v>
       </c>
@@ -8807,7 +8806,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>37</v>
       </c>
@@ -8830,7 +8829,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>37</v>
       </c>
@@ -8853,7 +8852,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>37</v>
       </c>
@@ -8899,7 +8898,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>9</v>
       </c>
@@ -8922,7 +8921,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>9</v>
       </c>
@@ -8945,7 +8944,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>58</v>
       </c>
@@ -8968,7 +8967,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>58</v>
       </c>
@@ -8991,7 +8990,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>97</v>
       </c>
@@ -9014,7 +9013,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>97</v>
       </c>
@@ -9060,7 +9059,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>7</v>
       </c>
@@ -9083,7 +9082,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>7</v>
       </c>
@@ -9106,7 +9105,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>54</v>
       </c>
@@ -9129,7 +9128,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>54</v>
       </c>
@@ -9152,7 +9151,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>41</v>
       </c>
@@ -9175,7 +9174,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>41</v>
       </c>
@@ -9198,7 +9197,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>100</v>
       </c>
@@ -9221,7 +9220,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>100</v>
       </c>
@@ -9244,7 +9243,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>98</v>
       </c>
@@ -9267,7 +9266,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>98</v>
       </c>
@@ -9315,9 +9314,16 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:G139" xr:uid="{00000000-0001-0000-0100-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G139">
-      <sortCondition ref="A1:A139"/>
-    </sortState>
+    <filterColumn colId="1">
+      <filters>
+        <filter val="1"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="5">
+      <filters>
+        <filter val="TRUE"/>
+      </filters>
+    </filterColumn>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
